--- a/GroiroServices/services/reports/ibts_-.xlsx
+++ b/GroiroServices/services/reports/ibts_-.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,49 +456,305 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45256</v>
+        <v>45334</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Печать</t>
+          <t>Печать А4</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45231</v>
+        <v>45334</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Копирование</t>
+          <t>Запись на флешку</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1231</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="2" t="n">
+        <v>45334</v>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Запись на флешку</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>45334</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Запись на флешку</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Запись на флешку</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Отправка по e-mail</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Запись на флешку</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45340</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45293</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45380</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Отправка по e-mail</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.96</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45260</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Печать А4</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Итого:</t>
         </is>
       </c>
-      <c r="C4">
-        <f>SUM(C2:C3)</f>
+      <c r="C20">
+        <f>SUM(C2:C19)</f>
         <v/>
       </c>
-      <c r="D4">
-        <f>SUM(D2:D3)</f>
+      <c r="D20">
+        <f>SUM(D2:D19)</f>
         <v/>
       </c>
     </row>
